--- a/AAII_Financials/Quarterly/RCRUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RCRUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
   <si>
     <t>RCRUY</t>
   </si>
@@ -656,73 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
-        <v>45657</v>
-      </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -759,8 +772,17 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -797,8 +819,17 @@
       <c r="N9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +866,17 @@
       <c r="N10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,8 +891,11 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -889,8 +932,17 @@
       <c r="N12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,8 +979,17 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -965,8 +1026,17 @@
       <c r="N14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1073,17 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,8 +1095,11 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1054,8 +1136,17 @@
       <c r="N17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1092,8 +1183,17 @@
       <c r="N18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,8 +1208,11 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1146,8 +1249,17 @@
       <c r="N20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1184,8 +1296,17 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1222,8 +1343,17 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1260,8 +1390,17 @@
       <c r="N23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1298,8 +1437,17 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,8 +1484,17 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1374,8 +1531,17 @@
       <c r="N26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1412,8 +1578,17 @@
       <c r="N27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,8 +1625,17 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1488,8 +1672,17 @@
       <c r="N29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1719,17 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,8 +1766,17 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1602,8 +1813,17 @@
       <c r="N32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1640,8 +1860,17 @@
       <c r="N33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,8 +1907,17 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1716,51 +1954,69 @@
       <c r="N35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
-        <v>45657</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +2031,11 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,46 +2050,58 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>4</v>
+      <c r="D41" s="3">
+        <v>5248100</v>
       </c>
       <c r="E41" s="3">
+        <v>4563200</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3615800</v>
+      </c>
+      <c r="G41" s="3">
+        <v>3533000</v>
+      </c>
+      <c r="H41" s="3">
         <v>5399900</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5288800</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7516200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3">
+        <v>7516200</v>
+      </c>
+      <c r="M41" s="3">
         <v>7392700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>7271700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>6679400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>6600000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>6179600</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1867,46 +2138,64 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>4</v>
+      <c r="D43" s="3">
+        <v>3915700</v>
       </c>
       <c r="E43" s="3">
+        <v>4020400</v>
+      </c>
+      <c r="F43" s="3">
+        <v>3874700</v>
+      </c>
+      <c r="G43" s="3">
+        <v>3900300</v>
+      </c>
+      <c r="H43" s="3">
         <v>3773500</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3771700</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3635000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="3">
+        <v>3635000</v>
+      </c>
+      <c r="M43" s="3">
         <v>3709900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>3405000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>3653600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>3968600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="Q43" s="3">
         <v>4082500</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1943,198 +2232,252 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>4</v>
+      <c r="D45" s="3">
+        <v>1215100</v>
       </c>
       <c r="E45" s="3">
+        <v>1197000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1020800</v>
+      </c>
+      <c r="G45" s="3">
+        <v>934700</v>
+      </c>
+      <c r="H45" s="3">
         <v>645600</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>767600</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>502900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
+        <v>502900</v>
+      </c>
+      <c r="M45" s="3">
         <v>630100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>477200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>569400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>454500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="Q45" s="3">
         <v>579200</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>4</v>
+      <c r="D46" s="3">
+        <v>10378800</v>
       </c>
       <c r="E46" s="3">
+        <v>9780600</v>
+      </c>
+      <c r="F46" s="3">
+        <v>8511300</v>
+      </c>
+      <c r="G46" s="3">
+        <v>8367900</v>
+      </c>
+      <c r="H46" s="3">
         <v>9819000</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>9828100</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11654100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L46" s="3">
+        <v>11654100</v>
+      </c>
+      <c r="M46" s="3">
         <v>11732800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>11153900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>10902400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>11023100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>10841300</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>4</v>
+      <c r="D47" s="3">
+        <v>12400</v>
       </c>
       <c r="E47" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1280100</v>
+      </c>
+      <c r="G47" s="3">
+        <v>90100</v>
+      </c>
+      <c r="H47" s="3">
         <v>116700</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1529700</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>177500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
+        <v>177500</v>
+      </c>
+      <c r="M47" s="3">
         <v>1888800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>1828000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>1883400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>202900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="Q47" s="3">
         <v>1773200</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>4</v>
+      <c r="D48" s="3">
+        <v>1123200</v>
       </c>
       <c r="E48" s="3">
+        <v>1209800</v>
+      </c>
+      <c r="F48" s="3">
+        <v>1310000</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1377900</v>
+      </c>
+      <c r="H48" s="3">
         <v>1398800</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1407700</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1566100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
+        <v>1566100</v>
+      </c>
+      <c r="M48" s="3">
         <v>1677600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>1635000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>1762300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>1926000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>1965000</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>4</v>
+      <c r="D49" s="3">
+        <v>4446700</v>
       </c>
       <c r="E49" s="3">
+        <v>4506700</v>
+      </c>
+      <c r="F49" s="3">
+        <v>4678000</v>
+      </c>
+      <c r="G49" s="3">
+        <v>4721900</v>
+      </c>
+      <c r="H49" s="3">
         <v>4561700</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4696400</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4600600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L49" s="3">
+        <v>4600600</v>
+      </c>
+      <c r="M49" s="3">
         <v>4819900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>4715600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>4798300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>4894200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="Q49" s="3">
         <v>4985800</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2514,17 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2561,64 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>4</v>
+      <c r="D52" s="3">
+        <v>942200</v>
       </c>
       <c r="E52" s="3">
+        <v>939200</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>1218900</v>
+      </c>
+      <c r="H52" s="3">
         <v>1167300</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>1446800</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>1446800</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>1753000</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2655,64 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>4</v>
+      <c r="D54" s="3">
+        <v>17900500</v>
       </c>
       <c r="E54" s="3">
+        <v>17540400</v>
+      </c>
+      <c r="F54" s="3">
+        <v>17244500</v>
+      </c>
+      <c r="G54" s="3">
+        <v>17302500</v>
+      </c>
+      <c r="H54" s="3">
         <v>18512800</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>18936600</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20790400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L54" s="3">
+        <v>20790400</v>
+      </c>
+      <c r="M54" s="3">
         <v>21426100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>20516400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>20437800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>21012500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="Q54" s="3">
         <v>20540800</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2727,11 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,236 +2746,293 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>4</v>
+      <c r="D57" s="3">
+        <v>2374600</v>
       </c>
       <c r="E57" s="3">
+        <v>549700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2353100</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2436700</v>
+      </c>
+      <c r="H57" s="3">
         <v>558700</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2268800</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>506100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
+        <v>506100</v>
+      </c>
+      <c r="M57" s="3">
         <v>2285000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>2069000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>2141500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>557900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>2397500</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>4</v>
+      <c r="D58" s="3">
+        <v>277000</v>
       </c>
       <c r="E58" s="3">
+        <v>276800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>259800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>290900</v>
+      </c>
+      <c r="H58" s="3">
         <v>296900</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>303000</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>295000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L58" s="3">
+        <v>295000</v>
+      </c>
+      <c r="M58" s="3">
         <v>435100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>417300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>544500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>564300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
         <v>513500</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>4</v>
+      <c r="D59" s="3">
+        <v>2316100</v>
       </c>
       <c r="E59" s="3">
+        <v>2904100</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2422100</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2526000</v>
+      </c>
+      <c r="H59" s="3">
         <v>2892600</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2498400</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2689400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
+        <v>2689400</v>
+      </c>
+      <c r="M59" s="3">
         <v>2205800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>2192600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>2176000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>3036000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="Q59" s="3">
         <v>2771300</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>4</v>
+      <c r="D60" s="3">
+        <v>4967700</v>
       </c>
       <c r="E60" s="3">
+        <v>5504900</v>
+      </c>
+      <c r="F60" s="3">
+        <v>5035000</v>
+      </c>
+      <c r="G60" s="3">
+        <v>5253500</v>
+      </c>
+      <c r="H60" s="3">
         <v>5356900</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5070200</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5017200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L60" s="3">
+        <v>5017200</v>
+      </c>
+      <c r="M60" s="3">
         <v>4925900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>4678800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>4862000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>5888500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>5682300</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>823100</v>
       </c>
       <c r="E61" s="3">
+        <v>894700</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1013700</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1079100</v>
+      </c>
+      <c r="H61" s="3">
         <v>1098400</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1067200</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1167000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>1167000</v>
+      </c>
+      <c r="M61" s="3">
         <v>1200500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>1156300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>1228800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>1353600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="Q61" s="3">
         <v>1428800</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
+      <c r="D62" s="3">
+        <v>180000</v>
       </c>
       <c r="E62" s="3">
+        <v>180000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>168200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>168800</v>
+      </c>
+      <c r="H62" s="3">
         <v>162600</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>162600</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>157400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
+        <v>157400</v>
+      </c>
+      <c r="M62" s="3">
         <v>146500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>153000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>152400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>156100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>168700</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +3069,17 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +3116,17 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +3163,64 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>4</v>
+      <c r="D66" s="3">
+        <v>6902300</v>
       </c>
       <c r="E66" s="3">
+        <v>7512100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>7233700</v>
+      </c>
+      <c r="G66" s="3">
+        <v>7562000</v>
+      </c>
+      <c r="H66" s="3">
         <v>7645500</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7427000</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7508800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L66" s="3">
+        <v>7508800</v>
+      </c>
+      <c r="M66" s="3">
         <v>7472800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>7186200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>7465000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>8668500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>8507100</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +3235,11 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +3276,17 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +3323,17 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3370,17 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3417,64 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>4</v>
+      <c r="D72" s="3">
+        <v>9570300</v>
       </c>
       <c r="E72" s="3">
+        <v>8622800</v>
+      </c>
+      <c r="F72" s="3">
+        <v>12470100</v>
+      </c>
+      <c r="G72" s="3">
+        <v>11872800</v>
+      </c>
+      <c r="H72" s="3">
         <v>10727000</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>14433200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12457500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
+        <v>12457500</v>
+      </c>
+      <c r="M72" s="3">
         <v>14182800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>12818000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>12452800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>12873700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>12724500</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3511,17 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3558,17 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3605,64 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>4</v>
+      <c r="D76" s="3">
+        <v>10918100</v>
       </c>
       <c r="E76" s="3">
+        <v>9957700</v>
+      </c>
+      <c r="F76" s="3">
+        <v>9933600</v>
+      </c>
+      <c r="G76" s="3">
+        <v>9661800</v>
+      </c>
+      <c r="H76" s="3">
         <v>10802000</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>11439500</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13228800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3">
+        <v>13228800</v>
+      </c>
+      <c r="M76" s="3">
         <v>13836300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>13221300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>12865000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>12239200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>11929200</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,51 +3699,69 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
-        <v>45657</v>
-      </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3212,8 +3798,17 @@
       <c r="N81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,46 +3823,58 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3">
+        <v>-80300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>189400</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3">
         <v>209900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>194700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>194100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-67200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
+        <v>194100</v>
+      </c>
+      <c r="L83" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="M83" s="3">
         <v>236400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="N83" s="3">
         <v>210800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>221100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>-85200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="Q83" s="3">
         <v>265700</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3911,17 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3958,17 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +4005,17 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +4052,17 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,46 +4099,64 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>4</v>
+      <c r="D89" s="3">
+        <v>1252900</v>
       </c>
       <c r="E89" s="3">
+        <v>1377600</v>
+      </c>
+      <c r="F89" s="3">
+        <v>970800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>849300</v>
+      </c>
+      <c r="H89" s="3">
         <v>1153400</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>1056800</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M89" s="3">
         <v>815800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>1274700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>377300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>747000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>846300</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,46 +4171,58 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
+      <c r="D91" s="3">
+        <v>-10900</v>
       </c>
       <c r="E91" s="3">
+        <v>-17100</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-27700</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="H91" s="3">
         <v>-12900</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-17500</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M91" s="3">
         <v>-20400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-27000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-17300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-39900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="Q91" s="3">
         <v>-58900</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +4259,17 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,46 +4306,64 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>4</v>
+      <c r="D94" s="3">
+        <v>-205800</v>
       </c>
       <c r="E94" s="3">
+        <v>44500</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-132600</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-288700</v>
+      </c>
+      <c r="H94" s="3">
         <v>-120400</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-97800</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M94" s="3">
         <v>-117000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-135100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-100500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-142000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-153500</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,28 +4378,31 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>4</v>
+      <c r="D96" s="3">
+        <v>106600</v>
       </c>
       <c r="E96" s="3">
+        <v>400</v>
+      </c>
+      <c r="F96" s="3">
+        <v>800</v>
+      </c>
+      <c r="G96" s="3">
+        <v>121100</v>
+      </c>
+      <c r="H96" s="3">
         <v>200</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
+      <c r="I96" s="3">
+        <v>900</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>4</v>
@@ -3710,14 +4413,23 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>300</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +4466,17 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4513,17 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,118 +4560,154 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>4</v>
+      <c r="D100" s="3">
+        <v>-428900</v>
       </c>
       <c r="E100" s="3">
+        <v>-691800</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-762200</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-2410000</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1135800</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-3351300</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M100" s="3">
         <v>-640600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>-554300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-198100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>-159700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>-1353000</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="D101" s="3">
+        <v>-319200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-775200</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3">
         <v>-370500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>220600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>532400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>24500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
+        <v>532400</v>
+      </c>
+      <c r="L101" s="3">
+        <v>24500</v>
+      </c>
+      <c r="M101" s="3">
         <v>-498200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>315900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>523200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>276500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>132500</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>784200</v>
       </c>
       <c r="E102" s="3">
+        <v>837300</v>
+      </c>
+      <c r="F102" s="3">
+        <v>171500</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-2071800</v>
+      </c>
+      <c r="H102" s="3">
         <v>-422000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-3167500</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-312300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>805900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>611200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>469800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>-1158400</v>
       </c>
     </row>
